--- a/erp-server/erp-server-file/src/main/resources/excel/plm/assetNotice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/assetNotice.xlsx
@@ -77,10 +77,10 @@
     <t>{.createPoTypeName}</t>
   </si>
   <si>
+    <t>{.assetCode}</t>
+  </si>
+  <si>
     <t>{.assetName}</t>
-  </si>
-  <si>
-    <t>{.chargeName}</t>
   </si>
   <si>
     <t>{.supplierName}</t>
@@ -1259,13 +1259,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="31.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="24.125" style="1" customWidth="1"/>
